--- a/dataset_t6_grouped/results2/G4/G4_T5171_W0014F0002T0006Z000C1N14_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T5171_W0014F0002T0006Z000C1N14_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>38.24384659681243</v>
+        <v>6.21462507198202</v>
       </c>
       <c r="D2" t="n">
-        <v>41.18300415455818</v>
+        <v>6.692238175115705</v>
       </c>
       <c r="E2" t="n">
-        <v>11.24370724372888</v>
+        <v>1.827102427105943</v>
       </c>
       <c r="F2" t="n">
-        <v>11.57286098164922</v>
+        <v>1.880589909517998</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>22.86437552475347</v>
+        <v>3.715461022772439</v>
       </c>
       <c r="D3" t="n">
-        <v>26.17410964986264</v>
+        <v>4.25329281810268</v>
       </c>
       <c r="E3" t="n">
-        <v>11.24370724372888</v>
+        <v>1.827102427105943</v>
       </c>
       <c r="F3" t="n">
-        <v>11.57286098164922</v>
+        <v>1.880589909517998</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>51.28623380379746</v>
+        <v>8.334012993117087</v>
       </c>
       <c r="D4" t="n">
-        <v>51.50242712727236</v>
+        <v>8.369144408181759</v>
       </c>
       <c r="E4" t="n">
-        <v>11.24370724372888</v>
+        <v>1.827102427105943</v>
       </c>
       <c r="F4" t="n">
-        <v>11.57286098164922</v>
+        <v>1.880589909517998</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>16.92220763113109</v>
+        <v>2.749858740058802</v>
       </c>
       <c r="D5" t="n">
-        <v>13.31352695569435</v>
+        <v>2.163448130300332</v>
       </c>
       <c r="E5" t="n">
-        <v>11.24370724372888</v>
+        <v>1.827102427105943</v>
       </c>
       <c r="F5" t="n">
-        <v>11.57286098164922</v>
+        <v>1.880589909517998</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>48.1790281291204</v>
+        <v>7.829092070982065</v>
       </c>
       <c r="D6" t="n">
-        <v>48.43249394416416</v>
+        <v>7.870280265926676</v>
       </c>
       <c r="E6" t="n">
-        <v>11.24370724372888</v>
+        <v>1.827102427105943</v>
       </c>
       <c r="F6" t="n">
-        <v>11.57286098164922</v>
+        <v>1.880589909517998</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>33.28429847465518</v>
+        <v>5.408698502131467</v>
       </c>
       <c r="D7" t="n">
-        <v>34.65544690232691</v>
+        <v>5.631510121628124</v>
       </c>
       <c r="E7" t="n">
-        <v>11.24370724372888</v>
+        <v>1.827102427105943</v>
       </c>
       <c r="F7" t="n">
-        <v>11.57286098164922</v>
+        <v>1.880589909517998</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>18.64452570543951</v>
+        <v>3.02973542713392</v>
       </c>
       <c r="D8" t="n">
-        <v>18.85887004210839</v>
+        <v>3.064566381842614</v>
       </c>
       <c r="E8" t="n">
-        <v>11.24370724372888</v>
+        <v>1.827102427105943</v>
       </c>
       <c r="F8" t="n">
-        <v>11.57286098164922</v>
+        <v>1.880589909517998</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>42.95798410575842</v>
+        <v>6.980672417185744</v>
       </c>
       <c r="D9" t="n">
-        <v>42.83347402578529</v>
+        <v>6.96043952919011</v>
       </c>
       <c r="E9" t="n">
-        <v>11.24370724372888</v>
+        <v>1.827102427105943</v>
       </c>
       <c r="F9" t="n">
-        <v>11.57286098164922</v>
+        <v>1.880589909517998</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>37.54472993049669</v>
+        <v>6.101018613705712</v>
       </c>
       <c r="D10" t="n">
-        <v>37.32168387012178</v>
+        <v>6.064773628894789</v>
       </c>
       <c r="E10" t="n">
-        <v>11.24370724372888</v>
+        <v>1.827102427105943</v>
       </c>
       <c r="F10" t="n">
-        <v>11.57286098164922</v>
+        <v>1.880589909517998</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>39.80093479093517</v>
+        <v>6.467651903526964</v>
       </c>
       <c r="D11" t="n">
-        <v>39.31662412203626</v>
+        <v>6.388951419830892</v>
       </c>
       <c r="E11" t="n">
-        <v>11.24370724372888</v>
+        <v>1.827102427105943</v>
       </c>
       <c r="F11" t="n">
-        <v>11.57286098164922</v>
+        <v>1.880589909517998</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>45.65872560866529</v>
+        <v>7.419542911408111</v>
       </c>
       <c r="D12" t="n">
-        <v>45.27025265842232</v>
+        <v>7.356416056993626</v>
       </c>
       <c r="E12" t="n">
-        <v>11.24370724372888</v>
+        <v>1.827102427105943</v>
       </c>
       <c r="F12" t="n">
-        <v>11.57286098164922</v>
+        <v>1.880589909517998</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
